--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,42 +459,26 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ServiceRequest.extension:interpretation</t>
-  </si>
-  <si>
-    <t>interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-interpretation-extension|0.1.0}
+    <t>ServiceRequest.extension:method</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-method-extension|0.1.0}
 </t>
   </si>
   <si>
-    <t>Interprétation</t>
-  </si>
-  <si>
-    <t>Extension permettant de spécifier une interprétation.</t>
+    <t>Méthode</t>
+  </si>
+  <si>
+    <t>Extension permettant d’indiquer la méthode utilisée : techniques biologiques (ex. : titration, agglutination…), techniques d’imagerie dans les demandes d'examen (ultrasound, tomographie, IRM…), des méthodes de mesure spécifiques, etc.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>ServiceRequest.extension:method</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-method-extension|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Méthode</t>
-  </si>
-  <si>
-    <t>Extension permettant d’indiquer la méthode utilisée : techniques biologiques (ex. : titration, agglutination…), techniques d’imagerie dans les demandes d'examen (ultrasound, tomographie, IRM…), des méthodes de mesure spécifiques, etc.</t>
-  </si>
-  <si>
     <t>ServiceRequest.extension:author</t>
   </si>
   <si>
@@ -1060,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Additional order information</t>
+    <t>Informations complémentaires sur la demande d'acte, par exemple : INR cible.</t>
   </si>
   <si>
     <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
@@ -1082,70 +1066,6 @@
     <t>NTE</t>
   </si>
   <si>
-    <t>ServiceRequest.orderDetail.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Résultat de la demande</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>ServiceRequest.quantity[x]</t>
   </si>
   <si>
@@ -1615,10 +1535,6 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:text}
-</t>
-  </si>
-  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1626,119 +1542,6 @@
   </si>
   <si>
     <t>ClinicalStatement.additionalText</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen</t>
-  </si>
-  <si>
-    <t>finaliteExamen</t>
-  </si>
-  <si>
-    <t>Finalité de l’examen demandé</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.author[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.author[x]</t>
-  </si>
-  <si>
-    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
-string</t>
-  </si>
-  <si>
-    <t>Individual responsible for the annotation</t>
-  </si>
-  <si>
-    <t>The individual responsible for making the annotation.</t>
-  </si>
-  <si>
-    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
-  </si>
-  <si>
-    <t>Annotation.author[x]</t>
-  </si>
-  <si>
-    <t>Act.participant[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.time</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.time</t>
-  </si>
-  <si>
-    <t>When the annotation was made</t>
-  </si>
-  <si>
-    <t>Indicates when this particular annotation was made.</t>
-  </si>
-  <si>
-    <t>Annotation.time</t>
-  </si>
-  <si>
-    <t>Act.effectiveTime</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.text</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">markdown
-</t>
-  </si>
-  <si>
-    <t>Finalité de l’examen</t>
-  </si>
-  <si>
-    <t>The text of the annotation in markdown format.</t>
-  </si>
-  <si>
-    <t>Annotation.text</t>
-  </si>
-  <si>
-    <t>Act.text</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande</t>
-  </si>
-  <si>
-    <t>justificationDemande</t>
-  </si>
-  <si>
-    <t>Justification de la demande d’examen</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.author[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.time</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.text</t>
-  </si>
-  <si>
-    <t>Justification de la demande d'examen</t>
   </si>
   <si>
     <t>ServiceRequest.patientInstruction</t>
@@ -2091,12 +1894,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO82"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.5" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.7265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3207,7 +3010,7 @@
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>91</v>
@@ -3306,7 +3109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3327,7 +3130,7 @@
         <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>81</v>
@@ -3428,11 +3231,9 @@
         <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C12" t="s" s="2">
         <v>154</v>
       </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3510,19 +3311,19 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>81</v>
@@ -3531,7 +3332,7 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -3542,10 +3343,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3553,10 +3354,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3568,13 +3369,13 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3613,31 +3414,31 @@
         <v>81</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>81</v>
@@ -3646,7 +3447,7 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3660,18 +3461,20 @@
         <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>167</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -3728,19 +3531,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3772,20 +3575,18 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3800,13 +3601,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3857,19 +3658,19 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
@@ -3878,7 +3679,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3889,10 +3690,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3903,7 +3704,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3915,13 +3716,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3960,31 +3761,31 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -3993,7 +3794,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -4004,10 +3805,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4015,10 +3816,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4030,22 +3831,24 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>81</v>
@@ -4075,31 +3878,31 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -4108,7 +3911,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -4119,10 +3922,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4130,7 +3933,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
@@ -4145,27 +3948,25 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N18" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>81</v>
@@ -4180,13 +3981,11 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4204,10 +4003,10 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>90</v>
@@ -4216,7 +4015,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4236,12 +4035,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4262,13 +4063,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4280,7 +4081,7 @@
         <v>81</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>81</v>
@@ -4295,11 +4096,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -4317,19 +4120,19 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4338,7 +4141,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4349,14 +4152,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4377,13 +4178,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4434,19 +4235,19 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4455,7 +4256,7 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4466,10 +4267,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4480,7 +4281,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4492,13 +4293,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4537,31 +4338,31 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4570,7 +4371,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4581,10 +4382,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4592,10 +4393,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4607,22 +4408,24 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>81</v>
@@ -4652,31 +4455,31 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4685,7 +4488,7 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4696,10 +4499,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4707,7 +4510,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4722,24 +4525,22 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N23" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>81</v>
@@ -4781,10 +4582,10 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4793,7 +4594,7 @@
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4813,18 +4614,20 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4839,13 +4642,13 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4896,19 +4699,19 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4917,7 +4720,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4928,20 +4731,18 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -4956,13 +4757,13 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5013,19 +4814,19 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -5034,7 +4835,7 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5045,10 +4846,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5059,7 +4860,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5071,13 +4872,13 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5116,31 +4917,31 @@
         <v>81</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5149,7 +4950,7 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5160,10 +4961,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5171,10 +4972,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5186,22 +4987,24 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>81</v>
@@ -5231,31 +5034,31 @@
         <v>81</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5264,7 +5067,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -5275,10 +5078,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5286,7 +5089,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
@@ -5301,24 +5104,22 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>81</v>
@@ -5360,10 +5161,10 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5372,7 +5173,7 @@
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5392,10 +5193,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5403,7 +5204,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
@@ -5418,22 +5219,24 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>81</v>
@@ -5475,10 +5278,10 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5487,7 +5290,7 @@
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5507,10 +5310,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5518,10 +5321,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5533,24 +5336,22 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N30" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>81</v>
@@ -5592,10 +5393,10 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>90</v>
@@ -5604,7 +5405,7 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5624,42 +5425,46 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5707,19 +5512,19 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5739,14 +5544,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5759,26 +5564,24 @@
         <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5814,19 +5617,17 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5838,32 +5639,34 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5872,7 +5675,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5884,16 +5687,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5931,17 +5734,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5956,31 +5761,29 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5989,7 +5792,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6001,16 +5804,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6060,7 +5863,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6075,27 +5878,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6118,16 +5921,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6177,7 +5980,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6192,13 +5995,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6216,7 +6019,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6235,17 +6038,15 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>244</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6309,13 +6110,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6326,14 +6127,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6352,13 +6153,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6409,7 +6210,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6424,13 +6225,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6441,21 +6242,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6467,16 +6268,20 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6524,13 +6329,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6539,13 +6344,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6556,18 +6361,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6576,26 +6381,24 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6619,13 +6422,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6643,10 +6446,10 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6658,27 +6461,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6692,7 +6495,7 @@
         <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>91</v>
@@ -6704,13 +6507,13 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6736,13 +6539,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6760,7 +6563,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>90</v>
@@ -6775,27 +6578,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>279</v>
+        <v>133</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6803,33 +6606,35 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6853,37 +6658,37 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>187</v>
+        <v>292</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6892,16 +6697,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6909,10 +6714,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6920,10 +6725,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6935,24 +6740,22 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q42" s="2"/>
+      <c r="Q42" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="R42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6972,37 +6775,37 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="Y42" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
@@ -7011,16 +6814,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7028,10 +6831,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7048,27 +6851,31 @@
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>81</v>
@@ -7089,31 +6896,31 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7128,113 +6935,109 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q44" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="R44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7249,38 +7052,38 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>91</v>
@@ -7292,16 +7095,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7327,13 +7130,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7351,46 +7154,46 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7400,7 +7203,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7409,18 +7212,18 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>197</v>
+        <v>338</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7444,13 +7247,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7468,16 +7271,16 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -7486,24 +7289,24 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7511,7 +7314,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7523,16 +7326,16 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>344</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>161</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7583,10 +7386,10 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>163</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7595,41 +7398,41 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>213</v>
+        <v>353</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7638,20 +7441,18 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7688,68 +7489,68 @@
         <v>81</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>169</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>358</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>164</v>
+        <v>359</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -7758,20 +7559,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7819,13 +7616,13 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
@@ -7834,27 +7631,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7877,20 +7674,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7914,13 +7707,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7938,7 +7731,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7956,28 +7749,28 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7996,18 +7789,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>367</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8055,7 +7846,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8070,41 +7861,41 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
@@ -8113,15 +7904,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8170,10 +7963,10 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>90</v>
@@ -8185,31 +7978,31 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>377</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8228,15 +8021,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8261,13 +8056,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8285,7 +8080,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8300,41 +8095,41 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>81</v>
@@ -8343,15 +8138,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8400,13 +8197,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8415,27 +8212,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8446,7 +8243,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8458,13 +8255,13 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8491,13 +8288,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8515,13 +8312,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8536,32 +8333,32 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8573,13 +8370,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8630,13 +8427,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8645,41 +8442,41 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AO56" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
@@ -8688,16 +8485,16 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>418</v>
+        <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8723,13 +8520,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8747,13 +8544,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -8762,38 +8559,38 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>428</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8805,16 +8602,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>197</v>
+        <v>442</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8840,13 +8637,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>433</v>
+        <v>81</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8864,13 +8661,13 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
@@ -8879,16 +8676,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8896,14 +8693,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8919,20 +8716,18 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -8981,7 +8776,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8996,16 +8791,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9013,14 +8808,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9036,18 +8831,20 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>197</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9072,13 +8869,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9096,7 +8893,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9111,16 +8908,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9128,10 +8925,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9154,15 +8951,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9211,7 +9010,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9229,28 +9028,28 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9260,7 +9059,7 @@
         <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>81</v>
@@ -9269,18 +9068,20 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9304,13 +9105,11 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9328,7 +9127,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9343,27 +9142,27 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9377,26 +9176,24 @@
         <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9445,7 +9242,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9460,27 +9257,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>473</v>
+        <v>336</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9491,7 +9288,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9500,16 +9297,16 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>476</v>
+        <v>155</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9560,13 +9357,13 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
@@ -9575,13 +9372,13 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>479</v>
+        <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>480</v>
+        <v>336</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9592,14 +9389,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9618,16 +9415,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9677,7 +9474,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9692,1994 +9489,23 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>489</v>
+        <v>133</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="Y67" s="2"/>
-      <c r="Z67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AC68" s="2"/>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="D75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO82" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO82">
+  <autoFilter ref="A1:AO65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11689,7 +9515,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI81">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,6 +659,28 @@
   <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-ServiceRequest.reason|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>R5: Explanation/Justification for procedure or service additional types</t>
+  </si>
+  <si>
+    <t>R5: `ServiceRequest.reason` additional types (CodeableReference(http://hl7.org/fhir/StructureDefinition/Condition), CodeableReference(http://hl7.org/fhir/StructureDefinition/Observation), CodeableReference(http://hl7.org/fhir/StructureDefinition/DiagnosticReport), CodeableReference(http://hl7.org/fhir/StructureDefinition/DocumentReference), CodeableReference(http://hl7.org/fhir/StructureDefinition/DetectedIssue))</t>
+  </si>
+  <si>
+    <t>Element `ServiceRequest.reason` is mapped to FHIR R4 element `ServiceRequest.reasonCode` as `SourceIsBroaderThanTarget`.
+Element `ServiceRequest.reason` is mapped to FHIR R4 element `ServiceRequest.reasonReference` as `SourceIsBroaderThanTarget`.
+The mappings for `ServiceRequest.reason` do not cover the following types: CodeableReference.
+This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all. To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise, use `concept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](https://hl7.org/fhir/servicerequest-example-di.html).</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -1894,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.5" customWidth="true" bestFit="true"/>
@@ -5428,11 +5450,13 @@
         <v>207</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5445,26 +5469,24 @@
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O31" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5512,7 +5534,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5521,7 +5543,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>141</v>
@@ -5533,7 +5555,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5544,14 +5566,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5564,24 +5586,26 @@
         <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5617,17 +5641,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AC32" s="2"/>
-      <c r="AD32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5639,34 +5665,32 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5675,7 +5699,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5687,16 +5711,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5734,19 +5758,17 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5761,29 +5783,31 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5792,7 +5816,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -5804,16 +5828,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5863,7 +5887,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5878,27 +5902,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5921,16 +5945,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5980,7 +6004,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5995,13 +6019,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AM35" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6012,14 +6036,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6038,15 +6062,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6095,7 +6121,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6113,10 +6139,10 @@
         <v>247</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6127,14 +6153,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6153,13 +6179,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6210,7 +6236,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6225,13 +6251,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6242,21 +6268,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6268,20 +6294,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6329,13 +6351,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6344,13 +6366,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6361,18 +6383,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6381,24 +6403,26 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>221</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6422,13 +6446,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6446,10 +6470,10 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6461,27 +6485,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6495,7 +6519,7 @@
         <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>91</v>
@@ -6507,13 +6531,13 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6542,10 +6566,10 @@
         <v>182</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6563,7 +6587,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>90</v>
@@ -6578,27 +6602,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>133</v>
+        <v>280</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6606,35 +6630,33 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6658,13 +6680,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>292</v>
+        <v>182</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6682,13 +6704,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6697,27 +6719,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>295</v>
+        <v>133</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6728,10 +6750,10 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -6740,49 +6762,51 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="Y42" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="R42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6799,13 +6823,13 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
@@ -6814,16 +6838,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6831,10 +6855,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6851,59 +6875,55 @@
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q43" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6920,7 +6940,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6935,65 +6955,69 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I44" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>192</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="P44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q44" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7013,13 +7037,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7037,7 +7061,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7052,38 +7076,38 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>91</v>
@@ -7098,13 +7122,13 @@
         <v>192</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7130,13 +7154,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7154,56 +7178,56 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7212,18 +7236,18 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7247,13 +7271,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7271,16 +7295,16 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -7289,16 +7313,16 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>81</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7314,7 +7338,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7338,7 +7362,9 @@
         <v>346</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7389,7 +7415,7 @@
         <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7401,35 +7427,35 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7444,13 +7470,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7501,10 +7527,10 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7516,41 +7542,41 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL48" t="s" s="2">
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -7559,13 +7585,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7616,7 +7642,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7631,41 +7657,41 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL49" t="s" s="2">
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>81</v>
@@ -7674,13 +7700,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7707,13 +7733,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7731,7 +7757,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7746,31 +7772,31 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7789,13 +7815,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7822,13 +7848,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -7846,7 +7872,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7861,31 +7887,31 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL51" t="s" s="2">
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="B52" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7895,7 +7921,7 @@
         <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
@@ -7904,17 +7930,15 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7963,7 +7987,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7978,31 +8002,31 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8012,7 +8036,7 @@
         <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8021,16 +8045,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>398</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8056,13 +8080,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8080,7 +8104,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8095,38 +8119,38 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8138,16 +8162,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>414</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8173,13 +8197,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8197,13 +8221,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8212,16 +8236,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8229,14 +8253,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8255,15 +8279,17 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>420</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8288,13 +8314,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8312,7 +8338,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8327,16 +8353,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>426</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8370,10 +8396,10 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>429</v>
@@ -8403,13 +8429,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8448,10 +8474,10 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8459,10 +8485,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8485,17 +8511,15 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>434</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8520,13 +8544,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8544,7 +8568,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8559,16 +8583,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8576,10 +8600,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8602,16 +8626,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>442</v>
+        <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8637,13 +8661,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8661,7 +8685,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8676,16 +8700,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8693,10 +8717,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8716,18 +8740,20 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -8776,7 +8802,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8791,16 +8817,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>455</v>
-      </c>
       <c r="AN59" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -8808,14 +8834,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>457</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8834,17 +8860,15 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8893,7 +8917,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8908,13 +8932,13 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8925,14 +8949,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8948,19 +8972,19 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9010,7 +9034,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9025,31 +9049,31 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9059,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>81</v>
@@ -9068,20 +9092,18 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>472</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9105,11 +9127,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>479</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9127,7 +9151,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9145,28 +9169,28 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>81</v>
+        <v>479</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9182,19 +9206,23 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9218,13 +9246,11 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9242,7 +9268,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9257,27 +9283,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AL63" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AN63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO63" t="s" s="2">
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>488</v>
       </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9288,19 +9314,19 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>155</v>
+        <v>489</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>490</v>
@@ -9357,13 +9383,13 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
@@ -9372,27 +9398,27 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>81</v>
+        <v>492</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9403,7 +9429,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9412,20 +9438,18 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>494</v>
+        <v>155</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N65" t="s" s="2">
         <v>497</v>
       </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9474,13 +9498,13 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
@@ -9489,23 +9513,140 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM65" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO65" t="s" s="2">
+      <c r="AM66" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO65">
+  <autoFilter ref="A1:AO66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9515,7 +9656,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
